--- a/20:21/PLteamsData20:21_with_tight_schedule.xlsx
+++ b/20:21/PLteamsData20:21_with_tight_schedule.xlsx
@@ -1218,7 +1218,7 @@
         <v>7</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1410,7 +1410,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1442,7 +1442,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1474,7 +1474,7 @@
         <v>6</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1538,7 +1538,7 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1634,7 +1634,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1666,7 +1666,7 @@
         <v>5</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1730,7 +1730,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1794,7 +1794,7 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1890,7 +1890,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1986,7 +1986,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -2050,7 +2050,7 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2082,7 +2082,7 @@
         <v>7</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2114,7 +2114,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -2210,7 +2210,7 @@
         <v>7</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2473,7 +2473,7 @@
         <v>6</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -2633,7 +2633,7 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -2697,7 +2697,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2985,7 +2985,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -3049,7 +3049,7 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -3081,7 +3081,7 @@
         <v>5</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -3145,7 +3145,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -3177,7 +3177,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -3241,7 +3241,7 @@
         <v>6</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -3337,7 +3337,7 @@
         <v>6</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -3369,7 +3369,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -3465,7 +3465,7 @@
         <v>6</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -3920,7 +3920,7 @@
         <v>6</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3952,7 +3952,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -4144,7 +4144,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4208,7 +4208,7 @@
         <v>5</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4272,7 +4272,7 @@
         <v>5</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4560,7 +4560,7 @@
         <v>6</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -4624,7 +4624,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -5207,7 +5207,7 @@
         <v>6</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -5303,7 +5303,7 @@
         <v>6</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -5367,7 +5367,7 @@
         <v>5</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -5495,7 +5495,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -5591,7 +5591,7 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -5623,7 +5623,7 @@
         <v>6</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -5687,7 +5687,7 @@
         <v>5</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -5751,7 +5751,7 @@
         <v>6</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -5847,7 +5847,7 @@
         <v>7</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -5879,7 +5879,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -5911,7 +5911,7 @@
         <v>7</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -6007,7 +6007,7 @@
         <v>7</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6174,7 +6174,7 @@
         <v>5</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6462,7 +6462,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6494,7 +6494,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6590,7 +6590,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -6654,7 +6654,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -6686,7 +6686,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -6718,7 +6718,7 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6846,7 +6846,7 @@
         <v>5</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -6878,7 +6878,7 @@
         <v>5</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -6942,7 +6942,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -7006,7 +7006,7 @@
         <v>6</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -7102,7 +7102,7 @@
         <v>6</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -7134,7 +7134,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -7166,7 +7166,7 @@
         <v>5</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -7230,7 +7230,7 @@
         <v>6</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -7429,7 +7429,7 @@
         <v>5</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -7493,7 +7493,7 @@
         <v>5</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -7717,7 +7717,7 @@
         <v>6</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -7749,7 +7749,7 @@
         <v>6</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -7813,7 +7813,7 @@
         <v>5</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -7909,7 +7909,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -7941,7 +7941,7 @@
         <v>6</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7973,7 +7973,7 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -8037,7 +8037,7 @@
         <v>5</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -8069,7 +8069,7 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -8101,7 +8101,7 @@
         <v>5</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -8229,7 +8229,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -8293,7 +8293,7 @@
         <v>5</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -8357,7 +8357,7 @@
         <v>6</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -8485,7 +8485,7 @@
         <v>7</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -8684,7 +8684,7 @@
         <v>5</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -8748,7 +8748,7 @@
         <v>6</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -8908,7 +8908,7 @@
         <v>5</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -8972,7 +8972,7 @@
         <v>5</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -9196,7 +9196,7 @@
         <v>6</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -9228,7 +9228,7 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -9292,7 +9292,7 @@
         <v>6</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -9452,7 +9452,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -9484,7 +9484,7 @@
         <v>6</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -9580,7 +9580,7 @@
         <v>6</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -9644,7 +9644,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -9740,7 +9740,7 @@
         <v>6</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -10163,7 +10163,7 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -10227,7 +10227,7 @@
         <v>6</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -10259,7 +10259,7 @@
         <v>5</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -10611,7 +10611,7 @@
         <v>5</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -10707,7 +10707,7 @@
         <v>6</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -10771,7 +10771,7 @@
         <v>5</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -10835,7 +10835,7 @@
         <v>6</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -10899,7 +10899,7 @@
         <v>6</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -10995,7 +10995,7 @@
         <v>7</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -11418,7 +11418,7 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -11482,7 +11482,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -11578,7 +11578,7 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -11610,7 +11610,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -11674,7 +11674,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -11706,7 +11706,7 @@
         <v>5</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -11738,7 +11738,7 @@
         <v>5</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -11802,7 +11802,7 @@
         <v>6</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -11962,7 +11962,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -11994,7 +11994,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -12058,7 +12058,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -12154,7 +12154,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -12186,7 +12186,7 @@
         <v>7</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -12282,7 +12282,7 @@
         <v>7</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -12513,7 +12513,7 @@
         <v>7</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -12641,7 +12641,7 @@
         <v>5</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -12673,7 +12673,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -12705,7 +12705,7 @@
         <v>6</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -12737,7 +12737,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -12769,7 +12769,7 @@
         <v>5</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -12833,7 +12833,7 @@
         <v>6</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -13025,7 +13025,7 @@
         <v>6</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -13057,7 +13057,7 @@
         <v>7</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -13185,7 +13185,7 @@
         <v>6</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -13217,7 +13217,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -13281,7 +13281,7 @@
         <v>6</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -13345,7 +13345,7 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -13409,7 +13409,7 @@
         <v>6</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -13473,7 +13473,7 @@
         <v>5</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -13505,7 +13505,7 @@
         <v>7</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -13768,7 +13768,7 @@
         <v>5</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -13832,7 +13832,7 @@
         <v>5</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -13992,7 +13992,7 @@
         <v>6</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -14024,7 +14024,7 @@
         <v>6</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -14088,7 +14088,7 @@
         <v>6</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -14120,7 +14120,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -14184,7 +14184,7 @@
         <v>6</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -14216,7 +14216,7 @@
         <v>6</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -14248,7 +14248,7 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -14312,7 +14312,7 @@
         <v>6</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -14344,7 +14344,7 @@
         <v>6</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -14472,7 +14472,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -14632,7 +14632,7 @@
         <v>5</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -14664,7 +14664,7 @@
         <v>6</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -14696,7 +14696,7 @@
         <v>5</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -14728,7 +14728,7 @@
         <v>5</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -14760,7 +14760,7 @@
         <v>6</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -15183,7 +15183,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -15247,7 +15247,7 @@
         <v>6</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -15343,7 +15343,7 @@
         <v>6</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -15439,7 +15439,7 @@
         <v>6</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -15535,7 +15535,7 @@
         <v>6</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -15759,7 +15759,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -15823,7 +15823,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -15951,7 +15951,7 @@
         <v>5</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -16015,7 +16015,7 @@
         <v>6</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -16278,7 +16278,7 @@
         <v>6</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -16438,7 +16438,7 @@
         <v>5</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -16470,7 +16470,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -16502,7 +16502,7 @@
         <v>5</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -16822,7 +16822,7 @@
         <v>6</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -16854,7 +16854,7 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -16982,7 +16982,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -17014,7 +17014,7 @@
         <v>6</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -17110,7 +17110,7 @@
         <v>6</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -17142,7 +17142,7 @@
         <v>7</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -17174,7 +17174,7 @@
         <v>6</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -17238,7 +17238,7 @@
         <v>6</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -17270,7 +17270,7 @@
         <v>6</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -17693,7 +17693,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -17757,7 +17757,7 @@
         <v>5</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -17789,7 +17789,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -17853,7 +17853,7 @@
         <v>6</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -18013,7 +18013,7 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -18077,7 +18077,7 @@
         <v>6</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -18141,7 +18141,7 @@
         <v>5</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -18205,7 +18205,7 @@
         <v>6</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -18237,7 +18237,7 @@
         <v>6</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -18301,7 +18301,7 @@
         <v>5</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -18365,7 +18365,7 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -18429,7 +18429,7 @@
         <v>6</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -18525,7 +18525,7 @@
         <v>7</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -18788,7 +18788,7 @@
         <v>5</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -18980,7 +18980,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -19172,7 +19172,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -19236,7 +19236,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -19268,7 +19268,7 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -19300,7 +19300,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -19364,7 +19364,7 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -19396,7 +19396,7 @@
         <v>5</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -19524,7 +19524,7 @@
         <v>6</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -19620,7 +19620,7 @@
         <v>5</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -19652,7 +19652,7 @@
         <v>7</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -19780,7 +19780,7 @@
         <v>6</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -20043,7 +20043,7 @@
         <v>5</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -20267,7 +20267,7 @@
         <v>5</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -20395,7 +20395,7 @@
         <v>5</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -20459,7 +20459,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -20555,7 +20555,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -20587,7 +20587,7 @@
         <v>7</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -20651,7 +20651,7 @@
         <v>6</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -20683,7 +20683,7 @@
         <v>5</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -20747,7 +20747,7 @@
         <v>6</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -20779,7 +20779,7 @@
         <v>6</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -20907,7 +20907,7 @@
         <v>6</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -20939,7 +20939,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -21003,7 +21003,7 @@
         <v>6</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -21035,7 +21035,7 @@
         <v>5</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -21298,7 +21298,7 @@
         <v>6</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -21458,7 +21458,7 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -21490,7 +21490,7 @@
         <v>5</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -21554,7 +21554,7 @@
         <v>6</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -21650,7 +21650,7 @@
         <v>6</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -21714,7 +21714,7 @@
         <v>5</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -21778,7 +21778,7 @@
         <v>5</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -21810,7 +21810,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -21874,7 +21874,7 @@
         <v>5</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -22002,7 +22002,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -22034,7 +22034,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -22194,7 +22194,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -22290,7 +22290,7 @@
         <v>7</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -22489,7 +22489,7 @@
         <v>5</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -22873,7 +22873,7 @@
         <v>5</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -22937,7 +22937,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -23001,7 +23001,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -23257,7 +23257,7 @@
         <v>6</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -23289,7 +23289,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -23353,7 +23353,7 @@
         <v>6</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -23417,7 +23417,7 @@
         <v>6</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -23449,7 +23449,7 @@
         <v>7</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -23481,7 +23481,7 @@
         <v>7</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -23577,7 +23577,7 @@
         <v>7</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -24160,7 +24160,7 @@
         <v>6</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -24192,7 +24192,7 @@
         <v>6</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -24256,7 +24256,7 @@
         <v>5</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -24384,7 +24384,7 @@
         <v>5</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -24448,7 +24448,7 @@
         <v>5</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -24512,7 +24512,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -24608,7 +24608,7 @@
         <v>5</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -24704,7 +24704,7 @@
         <v>5</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -24832,7 +24832,7 @@
         <v>7</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -25095,7 +25095,7 @@
         <v>5</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -25159,7 +25159,7 @@
         <v>5</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -25191,7 +25191,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -25223,7 +25223,7 @@
         <v>5</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -25351,7 +25351,7 @@
         <v>5</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -25383,7 +25383,7 @@
         <v>6</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -25447,7 +25447,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -25511,7 +25511,7 @@
         <v>6</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -25543,7 +25543,7 @@
         <v>6</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -25575,7 +25575,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -25607,7 +25607,7 @@
         <v>7</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -25671,7 +25671,7 @@
         <v>5</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -25735,7 +25735,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -25831,7 +25831,7 @@
         <v>5</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -25895,7 +25895,7 @@
         <v>6</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -25927,7 +25927,7 @@
         <v>7</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -25959,7 +25959,7 @@
         <v>6</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -25991,7 +25991,7 @@
         <v>5</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -26055,7 +26055,7 @@
         <v>7</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
